--- a/docs/WiseTrader_Demo_Tracker.xlsx
+++ b/docs/WiseTrader_Demo_Tracker.xlsx
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:K11"/>
+  <dimension ref="A1:K12"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="8" customWidth="1" style="16" min="1" max="1"/>
@@ -523,93 +523,80 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" s="16" t="inlineStr">
+        <is>
+          <t>DEMO STARTED 2026-08-06 (confirmed with user 2026-08-07): v2.51 attached to the correct XAUUSD demo account, InpTestTag=DEMO_LIVE (journal now isolated at Common\Files\WiseTrader_XAUUSD_20260707_DEMO_LIVE.csv, separate from dev-terminal testing). Two inits 37s apart at 15:56 (98277.32 then 47842.35 equity) were an account switch mid-setup, confirmed by user - $47,842.35 on the SECOND init is the real starting balance. Week 1 Day 1 = 2026-08-06. Target completion (4 calendar weeks) = 2026-09-03. Go-live gate unchanged: cumulative expectancy &gt;= $3.75/trade over &gt;=20 demo trades AND 4 full weeks. All six F52-F57 movement-signal toggles confirmed OFF/default at launch (see CHANGELOG v2.51) - this is a clean A2_tuned run.</t>
+        </is>
+      </c>
+    </row>
     <row r="5" ht="23.85" customHeight="1" s="17">
-      <c r="A5" s="20" t="inlineStr">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1" s="17">
+      <c r="A6" s="20" t="inlineStr">
         <is>
           <t>Week</t>
         </is>
       </c>
-      <c r="B5" s="20" t="inlineStr">
+      <c r="B6" s="20" t="inlineStr">
         <is>
           <t>Start Date</t>
         </is>
       </c>
-      <c r="C5" s="20" t="inlineStr">
+      <c r="C6" s="20" t="inlineStr">
         <is>
           <t>End Date</t>
         </is>
       </c>
-      <c r="D5" s="20" t="inlineStr">
+      <c r="D6" s="20" t="inlineStr">
         <is>
           <t>Trades</t>
         </is>
       </c>
-      <c r="E5" s="20" t="inlineStr">
+      <c r="E6" s="20" t="inlineStr">
         <is>
           <t>Net P&amp;L</t>
         </is>
       </c>
-      <c r="F5" s="20" t="inlineStr">
+      <c r="F6" s="20" t="inlineStr">
         <is>
           <t>Win Rate</t>
         </is>
       </c>
-      <c r="G5" s="20" t="inlineStr">
+      <c r="G6" s="20" t="inlineStr">
         <is>
           <t>Expectancy</t>
         </is>
       </c>
-      <c r="H5" s="20" t="inlineStr">
+      <c r="H6" s="20" t="inlineStr">
         <is>
           <t>Cum. Trades</t>
         </is>
       </c>
-      <c r="I5" s="20" t="inlineStr">
+      <c r="I6" s="20" t="inlineStr">
         <is>
           <t>Cum. Net P&amp;L</t>
         </is>
       </c>
-      <c r="J5" s="20" t="inlineStr">
+      <c r="J6" s="20" t="inlineStr">
         <is>
           <t>Cum. Expectancy</t>
         </is>
       </c>
-      <c r="K5" s="20" t="inlineStr">
+      <c r="K6" s="20" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-    </row>
-    <row r="6" ht="15" customHeight="1" s="17">
-      <c r="A6" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="B6" s="21" t="n"/>
-      <c r="C6" s="21" t="n"/>
-      <c r="D6" s="21" t="n"/>
-      <c r="E6" s="22" t="n"/>
-      <c r="F6" s="23" t="n"/>
-      <c r="G6" s="24">
-        <f>IFERROR(E6/D6,"-")</f>
-        <v/>
-      </c>
-      <c r="H6" s="25">
-        <f>D6</f>
-        <v/>
-      </c>
-      <c r="I6" s="24">
-        <f>E6</f>
-        <v/>
-      </c>
-      <c r="J6" s="24">
-        <f>IFERROR(I6/H6,"-")</f>
-        <v/>
-      </c>
-      <c r="K6" s="26" t="n"/>
     </row>
     <row r="7" ht="15" customHeight="1" s="17">
       <c r="A7" s="21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B7" s="21" t="n"/>
       <c r="C7" s="21" t="n"/>
@@ -617,26 +604,26 @@
       <c r="E7" s="22" t="n"/>
       <c r="F7" s="23" t="n"/>
       <c r="G7" s="24">
-        <f>IFERROR(E7/D7,"-")</f>
+        <f>IFERROR(E6/D6,"-")</f>
         <v/>
       </c>
       <c r="H7" s="25">
-        <f>H6+D7</f>
+        <f>D6</f>
         <v/>
       </c>
       <c r="I7" s="24">
-        <f>I6+E7</f>
+        <f>E6</f>
         <v/>
       </c>
       <c r="J7" s="24">
-        <f>IFERROR(I7/H7,"-")</f>
+        <f>IFERROR(I6/H6,"-")</f>
         <v/>
       </c>
       <c r="K7" s="26" t="n"/>
     </row>
     <row r="8" ht="15" customHeight="1" s="17">
       <c r="A8" s="21" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B8" s="21" t="n"/>
       <c r="C8" s="21" t="n"/>
@@ -644,26 +631,26 @@
       <c r="E8" s="22" t="n"/>
       <c r="F8" s="23" t="n"/>
       <c r="G8" s="24">
-        <f>IFERROR(E8/D8,"-")</f>
+        <f>IFERROR(E7/D7,"-")</f>
         <v/>
       </c>
       <c r="H8" s="25">
-        <f>H7+D8</f>
+        <f>H6+D7</f>
         <v/>
       </c>
       <c r="I8" s="24">
-        <f>I7+E8</f>
+        <f>I6+E7</f>
         <v/>
       </c>
       <c r="J8" s="24">
-        <f>IFERROR(I8/H8,"-")</f>
+        <f>IFERROR(I7/H7,"-")</f>
         <v/>
       </c>
       <c r="K8" s="26" t="n"/>
     </row>
     <row r="9" ht="15" customHeight="1" s="17">
       <c r="A9" s="21" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B9" s="21" t="n"/>
       <c r="C9" s="21" t="n"/>
@@ -671,35 +658,63 @@
       <c r="E9" s="22" t="n"/>
       <c r="F9" s="23" t="n"/>
       <c r="G9" s="24">
+        <f>IFERROR(E8/D8,"-")</f>
+        <v/>
+      </c>
+      <c r="H9" s="25">
+        <f>H7+D8</f>
+        <v/>
+      </c>
+      <c r="I9" s="24">
+        <f>I7+E8</f>
+        <v/>
+      </c>
+      <c r="J9" s="24">
+        <f>IFERROR(I8/H8,"-")</f>
+        <v/>
+      </c>
+      <c r="K9" s="26" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="B10" s="21" t="n"/>
+      <c r="C10" s="21" t="n"/>
+      <c r="D10" s="21" t="n"/>
+      <c r="E10" s="22" t="n"/>
+      <c r="F10" s="23" t="n"/>
+      <c r="G10" s="24">
         <f>IFERROR(E9/D9,"-")</f>
         <v/>
       </c>
-      <c r="H9" s="25">
+      <c r="H10" s="25">
         <f>H8+D9</f>
         <v/>
       </c>
-      <c r="I9" s="24">
+      <c r="I10" s="24">
         <f>I8+E9</f>
         <v/>
       </c>
-      <c r="J9" s="24">
+      <c r="J10" s="24">
         <f>IFERROR(I9/H9,"-")</f>
         <v/>
       </c>
-      <c r="K9" s="26" t="n"/>
-    </row>
-    <row r="11" ht="15" customHeight="1" s="17">
-      <c r="A11" s="27" t="inlineStr">
+      <c r="K10" s="26" t="n"/>
+    </row>
+    <row r="11" ht="15" customHeight="1" s="17"/>
+    <row r="12">
+      <c r="A12" s="27" t="inlineStr">
         <is>
           <t>Gate check</t>
         </is>
       </c>
-      <c r="G11" s="27" t="inlineStr">
+      <c r="G12" s="27" t="inlineStr">
         <is>
           <t>Cum. expectancy &gt;= $3.75?</t>
         </is>
       </c>
-      <c r="H11" s="16">
+      <c r="H12" s="16">
         <f>IF(H9=0,"-",IF(I9/H9&gt;=3.75,"PASS","below target"))</f>
         <v/>
       </c>
